--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/OREGON_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/OREGON_2012.xlsx
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C121">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C590">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C683">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C724">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1019">
@@ -20413,7 +20413,7 @@
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1115">
